--- a/Tested_Models/Tested Models Results.xlsx
+++ b/Tested_Models/Tested Models Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381D6C3B-142D-4D97-B5DA-9953B5DA8F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C337478C-2CCD-4E62-9162-2D4F4C49F094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,47 @@
     <sheet name="Results of test models" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_26801F41_A4D7_436B_86BE_F48207894DBE_.wvu.FilterData" localSheetId="0" hidden="1">'Results of test models'!$A$1:$F$36</definedName>
+    <definedName name="Z_2820878D_77BC_421B_9B2E_2371EAD70769_.wvu.FilterData" localSheetId="0" hidden="1">'Results of test models'!$A$1:$F$33</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
-    <customWorkbookView name="Table1 filter view" guid="{26801F41-A4D7-436B-86BE-F48207894DBE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Table1 filter view" guid="{2820878D-77BC-421B-9B2E-2371EAD70769}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="26">
+  <si>
+    <t>Fanar-1-9B-Instruct</t>
+  </si>
+  <si>
+    <t>Flan-T5-Tashkeel-Small</t>
+  </si>
+  <si>
+    <t>Glonor-ByT5-Arabic</t>
+  </si>
+  <si>
+    <t>Moonlight-16B-A3B-Instruct</t>
+  </si>
+  <si>
+    <t>Qwen3.5-9B</t>
+  </si>
+  <si>
+    <t>Qwen3.5-4B</t>
+  </si>
+  <si>
+    <t>Qwen3.5-0.8B</t>
+  </si>
+  <si>
+    <t>gemma-3-1b-pt-10k-diacritization</t>
+  </si>
+  <si>
+    <t>Tashkeel-350M-v2</t>
+  </si>
+  <si>
+    <t>Fine-Tashkeel</t>
+  </si>
   <si>
     <t>DER_ce</t>
   </si>
@@ -46,85 +76,31 @@
     <t>Domain Track</t>
   </si>
   <si>
-    <t>DER_C</t>
-  </si>
-  <si>
-    <t>DER_NoC</t>
-  </si>
-  <si>
-    <t>WER_C</t>
-  </si>
-  <si>
-    <t>WER_NoC</t>
-  </si>
-  <si>
-    <t>Moonlight-16B-A3B-Instruct</t>
+    <t>aya-expanse-8b</t>
   </si>
   <si>
     <t>Mean (MSA + CA)</t>
   </si>
   <si>
-    <t>Claude-3-7-Sonnet-Latest</t>
-  </si>
-  <si>
-    <t>Fanar-1-9B-Instruct</t>
-  </si>
-  <si>
-    <t>aya-expanse-8b</t>
-  </si>
-  <si>
-    <t>gemini-flash-2.0</t>
-  </si>
-  <si>
-    <t>Flan-T5-Tashkeel-Small</t>
-  </si>
-  <si>
-    <t>Qwen/Qwen3.5-4B</t>
-  </si>
-  <si>
-    <t>gemma-2-9b</t>
-  </si>
-  <si>
-    <t>Qwen/Qwen3.5-9B</t>
-  </si>
-  <si>
-    <t>Glonor-ByT5-Arabic</t>
-  </si>
-  <si>
-    <t>SILMA-9B-Instruct-v1.0</t>
-  </si>
-  <si>
-    <t>gemma-3-1b-pt-10k-diacritization</t>
-  </si>
-  <si>
-    <t>aya-23-8B</t>
-  </si>
-  <si>
-    <t>GPT-4</t>
-  </si>
-  <si>
-    <t>Fine-Tashkeel</t>
-  </si>
-  <si>
-    <t>ALLaM-7B-Instruct</t>
-  </si>
-  <si>
-    <t>Sadeed</t>
-  </si>
-  <si>
-    <t>Tashkeel-350M-v2</t>
-  </si>
-  <si>
-    <t>Yehia-7B</t>
-  </si>
-  <si>
-    <t>google/gemma-4-E4B-it</t>
-  </si>
-  <si>
-    <t>jais-13B</t>
+    <t>gemma-4-E4B-it</t>
   </si>
   <si>
     <t>MSA (Modern)</t>
+  </si>
+  <si>
+    <t>Column 2</t>
+  </si>
+  <si>
+    <t>Column 3</t>
+  </si>
+  <si>
+    <t>Column 4</t>
+  </si>
+  <si>
+    <t>Column 5</t>
+  </si>
+  <si>
+    <t>Column 6</t>
   </si>
   <si>
     <t>CA (Classical)</t>
@@ -142,15 +118,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Times"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -174,7 +157,8 @@
       <name val="Times"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times"/>
     </font>
@@ -185,19 +169,19 @@
       <color rgb="FF1F1F1F"/>
       <name val="Times"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -207,8 +191,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFC1E4F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -231,49 +215,119 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="24">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFD4D4D4"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFD4D4D4"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC1E4F5"/>
+          <bgColor rgb="FFC1E4F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -317,40 +371,46 @@
     <dxf>
       <border>
         <left style="thin">
-          <color rgb="FF356854"/>
+          <color theme="4"/>
         </left>
         <right style="thin">
-          <color rgb="FF356854"/>
+          <color theme="4"/>
         </right>
         <top style="thin">
-          <color rgb="FF356854"/>
+          <color theme="4"/>
         </top>
         <bottom style="thin">
-          <color rgb="FF356854"/>
+          <color theme="4"/>
         </bottom>
+        <vertical style="thin">
+          <color rgb="FFD4D4D4"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFD4D4D4"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFC1E4F5"/>
+          <bgColor rgb="FFC1E4F5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -443,76 +503,76 @@
     <dxf>
       <border>
         <left style="thin">
-          <color theme="4"/>
+          <color rgb="FF356854"/>
         </left>
         <right style="thin">
-          <color theme="4"/>
+          <color rgb="FF356854"/>
         </right>
         <top style="thin">
-          <color theme="4"/>
+          <color rgb="FF356854"/>
         </top>
         <bottom style="thin">
-          <color theme="4"/>
+          <color rgb="FF356854"/>
         </bottom>
-        <vertical style="thin">
-          <color rgb="FFD4D4D4"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FFD4D4D4"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC1E4F5"/>
-          <bgColor rgb="FFC1E4F5"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="5">
-    <tableStyle name="Results of test models-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+  <tableStyles count="6">
+    <tableStyle name="Models to test-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="20"/>
+      <tableStyleElement type="headerRow" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="22"/>
+      <tableStyleElement type="secondRowStripe" dxfId="21"/>
+    </tableStyle>
+    <tableStyle name="Fine-Tuning Models-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" size="0" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="19"/>
       <tableStyleElement type="firstRowStripe" dxfId="18"/>
       <tableStyleElement type="secondRowStripe" dxfId="17"/>
     </tableStyle>
-    <tableStyle name="Fine-Tuning Models-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Fine-Tuning Models-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="wholeTable" size="0" dxfId="12"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
       <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
-    <tableStyle name="Models to test-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+    <tableStyle name="Results of test models-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
       <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
       <tableStyleElement type="headerRow" dxfId="11"/>
       <tableStyleElement type="firstRowStripe" dxfId="10"/>
       <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
-    <tableStyle name="Results of test models-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+    <tableStyle name="Results of test models-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
       <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
       <tableStyleElement type="headerRow" dxfId="7"/>
       <tableStyleElement type="firstRowStripe" dxfId="6"/>
       <tableStyleElement type="secondRowStripe" dxfId="5"/>
     </tableStyle>
-    <tableStyle name="Fine-Tuning Models-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+    <tableStyle name="Results of test models-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
       <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
       <tableStyleElement type="headerRow" dxfId="3"/>
       <tableStyleElement type="firstRowStripe" dxfId="2"/>
@@ -531,7 +591,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ours" displayName="Ours" ref="A1:F36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ours" displayName="Ours" ref="A1:F33">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="DER_ce"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DER_noce"/>
@@ -541,19 +601,6 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Domain Track"/>
   </tableColumns>
   <tableStyleInfo name="Results of test models-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Sadeed_Paper" displayName="Sadeed_Paper" ref="J1:N12">
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="DER_C"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="DER_NoC"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="WER_C"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="WER_NoC"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Model"/>
-  </tableColumns>
-  <tableStyleInfo name="Results of test models-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -755,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N1001"/>
+  <dimension ref="A1:O997"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.19921875" customWidth="1"/>
@@ -772,855 +819,933 @@
     <col min="12" max="12" width="22" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
     <col min="14" max="14" width="29.5" customWidth="1"/>
-    <col min="15" max="26" width="8.59765625" customWidth="1"/>
+    <col min="15" max="15" width="18.5" customWidth="1"/>
+    <col min="16" max="26" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>92.18</v>
+      </c>
+      <c r="B2" s="3">
+        <v>92.41</v>
+      </c>
+      <c r="C2" s="3">
+        <v>99.67</v>
+      </c>
+      <c r="D2" s="3">
+        <v>99.62</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>86.6</v>
+      </c>
+      <c r="B3" s="3">
+        <v>87.1</v>
+      </c>
+      <c r="C3" s="3">
+        <v>99.01</v>
+      </c>
+      <c r="D3" s="3">
+        <v>98.84</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="7"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>66.55</v>
+      </c>
+      <c r="B4" s="9">
+        <v>67.08</v>
+      </c>
+      <c r="C4" s="9">
+        <v>85.78</v>
+      </c>
+      <c r="D4" s="9">
+        <v>84.04</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="7"/>
+    </row>
+    <row r="5" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>58.29</v>
+      </c>
+      <c r="B5" s="3">
+        <v>59.43</v>
+      </c>
+      <c r="C5" s="3">
+        <v>79</v>
+      </c>
+      <c r="D5" s="3">
+        <v>75.22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="7"/>
+    </row>
+    <row r="6" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>39.78</v>
+      </c>
+      <c r="B6" s="3">
+        <v>41.92</v>
+      </c>
+      <c r="C6" s="3">
+        <v>59.44</v>
+      </c>
+      <c r="D6" s="3">
+        <v>55.69</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>99.38</v>
-      </c>
-      <c r="B2" s="3">
-        <v>99.31</v>
-      </c>
-      <c r="C2" s="3">
-        <v>98.68</v>
-      </c>
-      <c r="D2" s="3">
-        <v>98.5</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="6">
-        <v>1.3940999999999999</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0.76929999999999998</v>
-      </c>
-      <c r="L2" s="6">
-        <v>4.6718000000000002</v>
-      </c>
-      <c r="M2" s="6">
-        <v>2.3098000000000001</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>92.35</v>
-      </c>
-      <c r="B3" s="5">
-        <v>92.02</v>
-      </c>
-      <c r="C3" s="5">
-        <v>92.78</v>
-      </c>
-      <c r="D3" s="5">
-        <v>91.85</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="6">
-        <v>3.1926000000000001</v>
-      </c>
-      <c r="K3" s="6">
-        <v>2.3782999999999999</v>
-      </c>
-      <c r="L3" s="6">
-        <v>7.9942000000000002</v>
-      </c>
-      <c r="M3" s="6">
-        <v>5.5044000000000004</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>73.739999999999995</v>
-      </c>
-      <c r="B4" s="3">
-        <v>73.489999999999995</v>
-      </c>
-      <c r="C4" s="3">
-        <v>81.86</v>
-      </c>
-      <c r="D4" s="3">
-        <v>77.25</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="6">
-        <v>78.855999999999995</v>
-      </c>
-      <c r="K4" s="6">
-        <v>60.918799999999997</v>
-      </c>
-      <c r="L4" s="6">
-        <v>99.7928</v>
-      </c>
-      <c r="M4" s="6">
-        <v>99.589500000000001</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>55.19</v>
-      </c>
-      <c r="B5" s="3">
-        <v>55.44</v>
-      </c>
-      <c r="C5" s="3">
-        <v>65.930000000000007</v>
-      </c>
-      <c r="D5" s="3">
-        <v>60.49</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="6">
-        <v>78.656700000000001</v>
-      </c>
-      <c r="K5" s="6">
-        <v>60.710599999999999</v>
-      </c>
-      <c r="L5" s="6">
-        <v>99.736699999999999</v>
-      </c>
-      <c r="M5" s="6">
-        <v>99.558599999999998</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
-        <v>41.58</v>
-      </c>
-      <c r="B6" s="9">
-        <v>42.26</v>
-      </c>
-      <c r="C6" s="9">
-        <v>47.98</v>
-      </c>
-      <c r="D6" s="9">
-        <v>44.26</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>41.35</v>
-      </c>
-      <c r="B7" s="5">
-        <v>39.479999999999997</v>
-      </c>
-      <c r="C7" s="5">
-        <v>48.76</v>
-      </c>
-      <c r="D7" s="5">
-        <v>42.58</v>
+      <c r="N6" s="7"/>
+    </row>
+    <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>50.25</v>
+      </c>
+      <c r="B7" s="3">
+        <v>50.66</v>
+      </c>
+      <c r="C7" s="3">
+        <v>55.81</v>
+      </c>
+      <c r="D7" s="3">
+        <v>52.95</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>33.619999999999997</v>
+      </c>
+      <c r="B8" s="9">
+        <v>33.22</v>
+      </c>
+      <c r="C8" s="9">
+        <v>50.68</v>
+      </c>
+      <c r="D8" s="9">
+        <v>44.77</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="7"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>26.14</v>
+      </c>
+      <c r="B9" s="9">
+        <v>26.35</v>
+      </c>
+      <c r="C9" s="9">
+        <v>31.48</v>
+      </c>
+      <c r="D9" s="9">
+        <v>28.81</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="12"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>17.91</v>
+      </c>
+      <c r="B10" s="3">
+        <v>17.73</v>
+      </c>
+      <c r="C10" s="3">
+        <v>22.61</v>
+      </c>
+      <c r="D10" s="3">
+        <v>20.350000000000001</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>6.33</v>
+      </c>
+      <c r="B11" s="3">
+        <v>5.64</v>
+      </c>
+      <c r="C11" s="3">
+        <v>15.28</v>
+      </c>
+      <c r="D11" s="3">
+        <v>10.4</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B12" s="15">
+        <v>3.61</v>
+      </c>
+      <c r="C12" s="9">
+        <v>11.86</v>
+      </c>
+      <c r="D12" s="9">
+        <v>7.88</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>4.18</v>
+      </c>
+      <c r="B13" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="C13" s="17">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="D13" s="17">
+        <v>6.78</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>88.36</v>
+      </c>
+      <c r="B16" s="3">
+        <v>88.37</v>
+      </c>
+      <c r="C16" s="3">
+        <v>99.37</v>
+      </c>
+      <c r="D16" s="3">
+        <v>99.3</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="6">
-        <v>25.627400000000002</v>
-      </c>
-      <c r="K7" s="6">
-        <v>19.758400000000002</v>
-      </c>
-      <c r="L7" s="6">
-        <v>47.4908</v>
-      </c>
-      <c r="M7" s="6">
-        <v>40.247799999999998</v>
-      </c>
-      <c r="N7" s="7" t="s">
+      <c r="K16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>24.98</v>
-      </c>
-      <c r="B8" s="5">
-        <v>24.72</v>
-      </c>
-      <c r="C8" s="5">
-        <v>29.58</v>
-      </c>
-      <c r="D8" s="5">
-        <v>26.78</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="6">
-        <v>3.8645</v>
-      </c>
-      <c r="K8" s="6">
-        <v>3.8645</v>
-      </c>
-      <c r="L8" s="6">
-        <v>5.2718999999999996</v>
-      </c>
-      <c r="M8" s="6">
-        <v>10.9274</v>
-      </c>
-      <c r="N8" s="7" t="s">
+      <c r="N16" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>19.059999999999999</v>
-      </c>
-      <c r="B9" s="3">
-        <v>18.8</v>
-      </c>
-      <c r="C9" s="3">
-        <v>22.52</v>
-      </c>
-      <c r="D9" s="3">
-        <v>20.25</v>
-      </c>
-      <c r="E9" s="3" t="s">
+    <row r="17" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>65.239999999999995</v>
+      </c>
+      <c r="B17" s="3">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="C17" s="3">
+        <v>86.62</v>
+      </c>
+      <c r="D17" s="3">
+        <v>84.8</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>64.94</v>
+      </c>
+      <c r="B18" s="3">
+        <v>65.27</v>
+      </c>
+      <c r="C18" s="3">
+        <v>70.86</v>
+      </c>
+      <c r="D18" s="3">
+        <v>67.69</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9">
+        <v>32.33</v>
+      </c>
+      <c r="B19" s="9">
+        <v>31.72</v>
+      </c>
+      <c r="C19" s="9">
+        <v>53.63</v>
+      </c>
+      <c r="D19" s="9">
+        <v>46.34</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="5"/>
+    </row>
+    <row r="20" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>31.87</v>
+      </c>
+      <c r="B20" s="9">
+        <v>31.83</v>
+      </c>
+      <c r="C20" s="9">
+        <v>37.76</v>
+      </c>
+      <c r="D20" s="9">
+        <v>34.58</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>14.81</v>
+      </c>
+      <c r="B21" s="3">
+        <v>14.57</v>
+      </c>
+      <c r="C21" s="3">
+        <v>21.18</v>
+      </c>
+      <c r="D21" s="3">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="5"/>
+    </row>
+    <row r="22" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="B22" s="3">
+        <v>7.33</v>
+      </c>
+      <c r="C22" s="3">
+        <v>20.97</v>
+      </c>
+      <c r="D22" s="3">
+        <v>14.93</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="5"/>
+    </row>
+    <row r="23" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9">
+        <v>5.3</v>
+      </c>
+      <c r="B23" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="C23" s="9">
+        <v>15.89</v>
+      </c>
+      <c r="D23" s="9">
+        <v>10.210000000000001</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+    </row>
+    <row r="24" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="F24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+    </row>
+    <row r="25" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="F25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+    </row>
+    <row r="26" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>84.83</v>
+      </c>
+      <c r="B26" s="3">
+        <v>85.83</v>
+      </c>
+      <c r="C26" s="3">
+        <v>98.65</v>
+      </c>
+      <c r="D26" s="3">
+        <v>98.39</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="6">
-        <v>50.358600000000003</v>
-      </c>
-      <c r="K9" s="6">
-        <v>39.409999999999997</v>
-      </c>
-      <c r="L9" s="6">
-        <v>70.3369</v>
-      </c>
-      <c r="M9" s="6">
-        <v>67.091999999999999</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>11.52</v>
-      </c>
-      <c r="B10" s="5">
-        <v>10.56</v>
-      </c>
-      <c r="C10" s="5">
-        <v>19.940000000000001</v>
-      </c>
-      <c r="D10" s="5">
-        <v>14.12</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>67.86</v>
+      </c>
+      <c r="B27" s="3">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="C27" s="3">
+        <v>84.95</v>
+      </c>
+      <c r="D27" s="3">
+        <v>83.27</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="6">
-        <v>7.2915000000000001</v>
-      </c>
-      <c r="K10" s="6">
-        <v>5.2625000000000002</v>
-      </c>
-      <c r="L10" s="6">
-        <v>13.7425</v>
-      </c>
-      <c r="M10" s="6">
-        <v>9.9245000000000001</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>7.56</v>
-      </c>
-      <c r="B11" s="3">
-        <v>6.49</v>
-      </c>
-      <c r="C11" s="3">
-        <v>14.53</v>
-      </c>
-      <c r="D11" s="3">
-        <v>9.65</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="6">
-        <v>50.880099999999999</v>
-      </c>
-      <c r="K11" s="6">
-        <v>39.767699999999998</v>
-      </c>
-      <c r="L11" s="6">
-        <v>70.232299999999995</v>
-      </c>
-      <c r="M11" s="6">
-        <v>67.152000000000001</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
-        <v>5.74</v>
-      </c>
-      <c r="B12" s="12">
-        <v>5.15</v>
-      </c>
-      <c r="C12" s="12">
-        <v>10.17</v>
-      </c>
-      <c r="D12" s="12">
-        <v>6.86</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="6">
-        <v>78.682000000000002</v>
-      </c>
-      <c r="K12" s="6">
-        <v>60.7271</v>
-      </c>
-      <c r="L12" s="6">
-        <v>99.754099999999994</v>
-      </c>
-      <c r="M12" s="6">
-        <v>99.5702</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>99.93</v>
-      </c>
-      <c r="B15" s="3">
-        <v>99.86</v>
-      </c>
-      <c r="C15" s="3">
-        <v>98.8</v>
-      </c>
-      <c r="D15" s="3">
-        <v>98.68</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>30.87</v>
-      </c>
-      <c r="B16" s="5">
-        <v>30.24</v>
-      </c>
-      <c r="C16" s="5">
-        <v>36.049999999999997</v>
-      </c>
-      <c r="D16" s="5">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>96.28</v>
-      </c>
-      <c r="B17" s="5">
-        <v>96.05</v>
-      </c>
-      <c r="C17" s="5">
-        <v>96.26</v>
-      </c>
-      <c r="D17" s="5">
-        <v>95.69</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
-        <v>11.14</v>
-      </c>
-      <c r="B18" s="5">
-        <v>9.9600000000000009</v>
-      </c>
-      <c r="C18" s="5">
-        <v>20.420000000000002</v>
-      </c>
-      <c r="D18" s="5">
-        <v>14.06</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>40.04</v>
-      </c>
-      <c r="B19" s="5">
-        <v>37.61</v>
-      </c>
-      <c r="C19" s="5">
-        <v>49.86</v>
-      </c>
-      <c r="D19" s="5">
-        <v>41.97</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>16.440000000000001</v>
-      </c>
-      <c r="B20" s="3">
-        <v>15.98</v>
-      </c>
-      <c r="C20" s="3">
-        <v>21.1</v>
-      </c>
-      <c r="D20" s="3">
-        <v>18.25</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="F27" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>10.97</v>
-      </c>
-      <c r="B21" s="3">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="C21" s="3">
-        <v>20.73</v>
-      </c>
-      <c r="D21" s="3">
-        <v>14.68</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>86.21</v>
-      </c>
-      <c r="B22" s="3">
-        <v>85.85</v>
-      </c>
-      <c r="C22" s="3">
-        <v>87.24</v>
-      </c>
-      <c r="D22" s="3">
-        <v>85.34</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
-        <v>50.72</v>
-      </c>
-      <c r="B23" s="9">
-        <v>51.2</v>
-      </c>
-      <c r="C23" s="9">
-        <v>58.92</v>
-      </c>
-      <c r="D23" s="9">
-        <v>54.39</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>98.83</v>
-      </c>
-      <c r="B26" s="3">
-        <v>98.76</v>
-      </c>
-      <c r="C26" s="3">
-        <v>98.56</v>
-      </c>
-      <c r="D26" s="3">
-        <v>98.32</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="B27" s="5">
-        <v>19.190000000000001</v>
-      </c>
-      <c r="C27" s="5">
-        <v>23.1</v>
-      </c>
-      <c r="D27" s="5">
-        <v>20.86</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
-        <v>88.42</v>
-      </c>
-      <c r="B28" s="5">
-        <v>87.99</v>
-      </c>
-      <c r="C28" s="5">
-        <v>89.3</v>
-      </c>
-      <c r="D28" s="5">
-        <v>88.02</v>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="5"/>
+    </row>
+    <row r="28" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9">
+        <v>34.92</v>
+      </c>
+      <c r="B28" s="9">
+        <v>34.72</v>
+      </c>
+      <c r="C28" s="9">
+        <v>47.73</v>
+      </c>
+      <c r="D28" s="9">
+        <v>43.2</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
-        <v>11.9</v>
-      </c>
-      <c r="B29" s="5">
-        <v>11.16</v>
-      </c>
-      <c r="C29" s="5">
-        <v>19.45</v>
-      </c>
-      <c r="D29" s="5">
-        <v>14.19</v>
+        <v>25</v>
+      </c>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>35.57</v>
+      </c>
+      <c r="B29" s="3">
+        <v>36.04</v>
+      </c>
+      <c r="C29" s="3">
+        <v>40.76</v>
+      </c>
+      <c r="D29" s="3">
+        <v>38.200000000000003</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
-        <v>42.66</v>
-      </c>
-      <c r="B30" s="5">
-        <v>41.35</v>
-      </c>
-      <c r="C30" s="5">
-        <v>47.66</v>
-      </c>
-      <c r="D30" s="5">
-        <v>43.18</v>
+        <v>25</v>
+      </c>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9">
+        <v>20.41</v>
+      </c>
+      <c r="B30" s="9">
+        <v>20.87</v>
+      </c>
+      <c r="C30" s="9">
+        <v>25.19</v>
+      </c>
+      <c r="D30" s="9">
+        <v>23.04</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+    </row>
+    <row r="31" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>21.67</v>
+        <v>21</v>
       </c>
       <c r="B31" s="3">
-        <v>21.63</v>
+        <v>20.89</v>
       </c>
       <c r="C31" s="3">
-        <v>23.95</v>
+        <v>24.04</v>
       </c>
       <c r="D31" s="3">
-        <v>22.25</v>
-      </c>
-      <c r="E31" s="3" t="s">
+        <v>22.37</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>4.1399999999999997</v>
+        <v>4.63</v>
       </c>
       <c r="B32" s="3">
-        <v>3.29</v>
+        <v>3.96</v>
       </c>
       <c r="C32" s="3">
-        <v>8.33</v>
+        <v>9.59</v>
       </c>
       <c r="D32" s="3">
-        <v>4.63</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>28</v>
+        <v>5.88</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
-        <v>83.41</v>
-      </c>
-      <c r="B33" s="3">
-        <v>82.93</v>
-      </c>
-      <c r="C33" s="3">
-        <v>85.22</v>
-      </c>
-      <c r="D33" s="3">
-        <v>83.46</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+    </row>
+    <row r="33" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="15">
+        <v>2.89</v>
+      </c>
+      <c r="B33" s="15">
+        <v>2.72</v>
+      </c>
+      <c r="C33" s="15">
+        <v>7.84</v>
+      </c>
+      <c r="D33" s="15">
+        <v>5.55</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>1</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
-        <v>28.72</v>
-      </c>
-      <c r="B34" s="9">
-        <v>29.03</v>
-      </c>
-      <c r="C34" s="9">
-        <v>34.89</v>
-      </c>
-      <c r="D34" s="9">
-        <v>32.1</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>25</v>
+      </c>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+    </row>
+    <row r="34" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+    </row>
+    <row r="35" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="5"/>
+    </row>
+    <row r="36" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="5"/>
+    </row>
+    <row r="37" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+    </row>
+    <row r="38" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+    </row>
+    <row r="39" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+    </row>
+    <row r="40" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+    </row>
+    <row r="41" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+    </row>
+    <row r="42" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+    </row>
+    <row r="43" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+    </row>
+    <row r="44" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+    </row>
+    <row r="45" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+    </row>
+    <row r="46" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="5"/>
+    </row>
+    <row r="47" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="5"/>
+    </row>
+    <row r="48" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+    </row>
+    <row r="49" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+    </row>
+    <row r="50" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="10:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2554,23 +2679,19 @@
     <row r="995" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="996" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="997" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{26801F41-A4D7-436B-86BE-F48207894DBE}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{2820878D-77BC-421B-9B2E-2371EAD70769}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F36" xr:uid="{8B3D97C4-0472-4AE5-9F99-C11C19070954}"/>
+      <autoFilter ref="A1:F33" xr:uid="{47AD16A3-41CE-4719-B746-D45AF8A11660}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="J2:M12 C2:D36" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>AND(ISNUMBER(C2),(NOT(OR(NOT(ISERROR(DATEVALUE(C2))), AND(ISNUMBER(C2), LEFT(CELL("format", C2))="D")))))</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="L18:M49 A2:D33 K17:L17 J2:J11 K2:M10" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="N2:N12" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F36" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation allowBlank="1" showDropDown="1" sqref="N2:N11 K11:M11" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
+    <dataValidation type="list" allowBlank="1" sqref="F2:F33 N17 O18:O49" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Mean (MSA + CA),MSA (Modern),CA (Classical)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2580,9 +2701,8 @@
     <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K008000 Public - عام&amp;1#_x000D_&amp;"Arial"&amp;11&amp;K000000008000 Public - عام#_x000D_</oddHeader>
     <oddFooter>&amp;C_x000D_#008000 Public - عام_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K008000 Public - عام</oddFooter>
   </headerFooter>
-  <tableParts count="2">
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
